--- a/3d_Printed_Frames/UCF/3D_UCF_parts.xlsx
+++ b/3d_Printed_Frames/UCF/3D_UCF_parts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RoseEngine\GitHub\3DPrinted_Working\UCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA13AFFB-7572-4E17-982D-FAB83E867E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72408AD5-CC2E-41F0-ACA0-0564992FDADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="16440" xr2:uid="{E6130C06-9D90-4F07-AC82-B241B14718F8}"/>
+    <workbookView xWindow="1335" yWindow="1275" windowWidth="25620" windowHeight="13725" xr2:uid="{E6130C06-9D90-4F07-AC82-B241B14718F8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>M3x6 Set screw</t>
   </si>
@@ -95,9 +95,6 @@
     <t>Double pulley spacer</t>
   </si>
   <si>
-    <t>Cutter head (Brass or steel optional)</t>
-  </si>
-  <si>
     <t>Round Poly belt: 2mm</t>
   </si>
   <si>
@@ -108,6 +105,21 @@
   </si>
   <si>
     <t>Metric Allen wrenches: 1.5, 3</t>
+  </si>
+  <si>
+    <t>Cutter head:  1/8" (Brass or steel optional)</t>
+  </si>
+  <si>
+    <t>Insert cutter head: CW</t>
+  </si>
+  <si>
+    <t>Insert cutter head: CCW</t>
+  </si>
+  <si>
+    <t>Sharpening jig: 1/8" 60 degrees</t>
+  </si>
+  <si>
+    <t>Sharpening jig: 1/8" 120 degrees</t>
   </si>
 </sst>
 </file>
@@ -491,7 +503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8088C4D-8B86-492D-8334-67A79002B133}">
-  <dimension ref="A2:B26"/>
+  <dimension ref="A2:B30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="41.28515625" customWidth="1"/>
@@ -606,12 +618,12 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -632,15 +644,15 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -648,25 +660,57 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B23" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>1</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>1</v>
+      </c>
+      <c r="B25" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>1</v>
+      </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>1</v>
+      </c>
+      <c r="B27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
